--- a/DIC_CORRECTED_QUALITATIVE_ANALYSIS.xlsx
+++ b/DIC_CORRECTED_QUALITATIVE_ANALYSIS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1886199\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/Research_Paper_Integrated_Human_Digital_Strategic_Risk_Coordination_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6743A8-2949-4858-967C-8C7EDCE28C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
